--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4937-2025 artfynd.xlsx
+++ b/artfynd/A 4937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128485888</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
